--- a/datos_asegurados_prueba.xlsx
+++ b/datos_asegurados_prueba.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vn59hva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vn59hva\Desktop\Asegurados-Automatizacion-WALMART-OmniOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2279F740-C837-4F7A-9F5C-F96EE5C50AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC5908A-0E78-405C-9885-9AF0E454E11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1B7269E1-4011-4D68-A24D-0C9AF710F0FD}"/>
   </bookViews>
@@ -506,6 +506,11 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
